--- a/htb_machines_UPDATE.xlsx
+++ b/htb_machines_UPDATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS\HTB-EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF624B1-3E4A-4CEE-9CB4-C58825337D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A511CA0-9FD0-4D8A-A85C-AB0C9DE969EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="249">
   <si>
     <t>Nombre</t>
   </si>
@@ -760,6 +760,18 @@
   </si>
   <si>
     <t>ctf, writeup, web, docker, cve, web, rce</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Support HackTheBox (Easy)</t>
+  </si>
+  <si>
+    <t>ctf, writeup, web, ad, smb, binary</t>
+  </si>
+  <si>
+    <t>https://app.hackthebox.com/machines/support</t>
   </si>
 </sst>
 </file>
@@ -889,7 +901,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -919,6 +931,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3042,15 +3057,33 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
+      <c r="A60" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F60" s="10">
+        <v>44772</v>
+      </c>
+      <c r="G60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -3212,10 +3245,11 @@
     <hyperlink ref="H48" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="H9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="H59" r:id="rId4" xr:uid="{9EA76FCF-3C41-4736-9794-A24657154ABF}"/>
+    <hyperlink ref="H60" r:id="rId5" xr:uid="{6760F95E-C528-45A1-828C-ACE1B850C4F1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>